--- a/TestData/LV_T1516_GiftLog_ClientGiftPreApprovalPageRecipientsExceedsYearlyGiftAllowance.xlsx
+++ b/TestData/LV_T1516_GiftLog_ClientGiftPreApprovalPageRecipientsExceedsYearlyGiftAllowance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D399BD3-4C21-4BF6-AE07-209DAFCCCB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9351D098-A734-44B7-BD03-907F15F1579D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -72,9 +72,6 @@
     <t>ContactName</t>
   </si>
   <si>
-    <t>Test External</t>
-  </si>
-  <si>
     <t>CongratulationsMsg</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
     <t>WARNING:The following gift recipients will exceed their yearly gift maximum if the submitted gifts are approved. This gift request is subject to approval by the Compliance Department. Do you still wish to submit these gifts?</t>
   </si>
   <si>
-    <t>Giorgia Cardia</t>
-  </si>
-  <si>
     <t>StandardTestCompany</t>
   </si>
   <si>
@@ -180,18 +174,6 @@
     <t>ContactTypesValue</t>
   </si>
   <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>External</t>
-  </si>
-  <si>
-    <t>testlast@mailinator.com</t>
-  </si>
-  <si>
-    <t>(541) 754-3010</t>
-  </si>
-  <si>
     <t>External Contact</t>
   </si>
   <si>
@@ -226,6 +208,24 @@
   </si>
   <si>
     <t>Contacts</t>
+  </si>
+  <si>
+    <t>Olivia Ricketts</t>
+  </si>
+  <si>
+    <t>Giftlog Contact</t>
+  </si>
+  <si>
+    <t>Giftlog</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>32141256987</t>
+  </si>
+  <si>
+    <t>vkumar0427@hl.com</t>
   </si>
 </sst>
 </file>
@@ -576,26 +576,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -611,12 +611,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -634,17 +634,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -676,7 +676,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>4</v>
@@ -685,7 +685,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>7</v>
@@ -703,16 +703,16 @@
         <v>1</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
@@ -720,16 +720,16 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -738,25 +738,25 @@
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -769,45 +769,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71607737-C7C9-466B-B424-409215616E00}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -828,12 +835,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -854,86 +861,86 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1516_GiftLog_ClientGiftPreApprovalPageRecipientsExceedsYearlyGiftAllowance.xlsx
+++ b/TestData/LV_T1516_GiftLog_ClientGiftPreApprovalPageRecipientsExceedsYearlyGiftAllowance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9351D098-A734-44B7-BD03-907F15F1579D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F94A5F-1A61-4DF8-B35B-9187867C6F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -210,9 +210,6 @@
     <t>Contacts</t>
   </si>
   <si>
-    <t>Olivia Ricketts</t>
-  </si>
-  <si>
     <t>Giftlog Contact</t>
   </si>
   <si>
@@ -226,6 +223,9 @@
   </si>
   <si>
     <t>vkumar0427@hl.com</t>
+  </si>
+  <si>
+    <t>Melissa Zatta</t>
   </si>
 </sst>
 </file>
@@ -583,8 +583,8 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>59</v>
+      <c r="A2" t="s">
+        <v>64</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -720,7 +720,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>41</v>
@@ -741,7 +741,7 @@
         <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>
@@ -802,16 +802,16 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
         <v>61</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="G2" t="s">
         <v>47</v>

--- a/TestData/LV_T1516_GiftLog_ClientGiftPreApprovalPageRecipientsExceedsYearlyGiftAllowance.xlsx
+++ b/TestData/LV_T1516_GiftLog_ClientGiftPreApprovalPageRecipientsExceedsYearlyGiftAllowance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F94A5F-1A61-4DF8-B35B-9187867C6F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5291FF91-DFFE-42DF-8DC7-C599C555A900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -225,7 +225,7 @@
     <t>vkumar0427@hl.com</t>
   </si>
   <si>
-    <t>Melissa Zatta</t>
+    <t>Julie Carthane</t>
   </si>
 </sst>
 </file>
@@ -568,13 +568,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>53</v>
       </c>
@@ -582,15 +582,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -607,14 +607,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBE23FE4-DDDD-4B9C-BBD1-ACC49BC86162}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -627,22 +627,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EBF7CCC-0EA4-459E-9359-186EE4ACABA8}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -655,23 +655,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="24.5546875" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -715,11 +715,11 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="150" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -768,16 +768,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71607737-C7C9-466B-B424-409215616E00}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -797,7 +797,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -828,17 +828,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C674870-7E16-4E86-8A92-4D6617DAF46E}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -851,15 +851,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -873,7 +873,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -887,7 +887,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -901,7 +901,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -915,7 +915,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -929,7 +929,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
